--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T09:23:28+00:00</t>
+    <t>2026-07-17T06:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:02:16+00:00</t>
+    <t>2026-08-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-list</t>
+    <t>http://hl7.org/fhir/StructureDefinition/List</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -728,7 +728,7 @@
 </t>
   </si>
   <si>
-    <t>Die Reihenfolge der Listeneinträge ist fachlich relevant und wird durch den Ersteller durch die Reihung der Eintries festgelegt.</t>
+    <t>Entries in the list</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -788,7 +788,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Eintrags</t>
+    <t>Status/Workflow information about this item</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -800,7 +800,13 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that provide further information about the reason and meaning of the item in the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-item-flag|4.0.1</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -1233,7 +1239,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.66015625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2334,7 +2340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2353,7 +2359,7 @@
         <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3956,7 +3962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>246</v>
       </c>
@@ -3969,13 +3975,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4021,11 +4027,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4066,10 +4074,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4092,70 +4100,70 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4164,13 +4172,13 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4178,10 +4186,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4207,14 +4215,14 @@
         <v>197</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4263,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4278,7 +4286,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4286,10 +4294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4312,13 +4320,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4369,7 +4377,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4384,7 +4392,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4392,10 +4400,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4421,16 +4429,16 @@
         <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4459,7 +4467,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4477,7 +4485,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4492,7 +4500,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:50:30+00:00</t>
+    <t>2026-08-28T05:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$36</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="312">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das AT e-Diagnose List-Profil leitet sich vom HL7-AT-Core-R4-Profil ab und dient der strukturierten Listung von Einträgen.</t>
+    <t>Das AT e-Diagnose List-Profil dient der strukturierten Listung von Einträgen.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}list-integrity:Die Liste darf nur Referenzen (List.entry.item) enthalten, die dem Code der Liste (List.code) entsprechen. {(code.coding.exists(system='http://loinc.org' and code='11450-4') implies entry.item.all(reference.matches('(^|/)Condition/'))) and (code.coding.exists(system='http://loinc.org' and code='47519-4') implies entry.item.all(reference.matches('(^|/)Procedure/'))) and (code.coding.exists(system='http://loinc.org' and code='48765-2') implies entry.item.all(reference.matches('(^|/)AllergyIntolerance/')))}list-emptyreason-required:Begründung für leere Liste ist erforderlich. {entry.empty() implies emptyReason.exists()}</t>
   </si>
   <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
@@ -467,7 +467,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste zur Integritätsprüfung beim Schreibvorgang.</t>
+    <t>Kein logischer Identifier für die Liste erforderlich.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -491,10 +491,16 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>current</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListStatusVS</t>
+    <t>The current state of the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
   </si>
   <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
@@ -506,7 +512,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -540,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t>Titel der Liste</t>
+    <t>Die Liste hat keinen Titel.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -590,7 +596,8 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die Liste erstellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Diagnose ist.</t>
+    <t>Patient, für den die Liste geführt wird, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer der e-Diagnose ist.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -615,7 +622,7 @@
 </t>
   </si>
   <si>
-    <t>Patientenkontakt</t>
+    <t>Es wird kein Behandlungskontext dokumentiert.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -634,7 +641,7 @@
 </t>
   </si>
   <si>
-    <t>Letzte Aktualisierung der Liste.</t>
+    <t>Datum der letzten Aktualisierung der Liste.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -663,7 +670,8 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die die Liste erstellt und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Diagnose des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur nachdem er Einträge gelöscht hat.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
+des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -684,7 +692,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge in der Liste.</t>
+    <t>Die Reihenfolge der Einträge wird über die List.entries durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -712,7 +720,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zur Liste.</t>
+    <t>Keine Freitext-Anmerkungen auf Listenebene.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -728,7 +736,7 @@
 </t>
   </si>
   <si>
-    <t>Entries in the list</t>
+    <t>Die Reihenfolge der Listeneinträge kann in die Fachanwendung zurückgeschrieben werden. Gleichzeitig kann die Sortierung in lokalen Systemen erfolgen.</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -788,7 +796,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Status/Workflow information about this item</t>
+    <t>Kennzeichnung des Status entsprechend Workflow nicht relevant.</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -816,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Eintrag zur Entfernung markiert wurde. Wird durch Flag 'removed' gelöst.</t>
+    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -841,7 +849,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste.</t>
+    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -856,11 +864,11 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-condition|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-procedure|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-allergyintolerance)
 </t>
   </si>
   <si>
-    <t>Referenz auf einen Eintrag. Zu klären: reicht ein List-Profil oder braucht es jeweils eines für die integren Listen, die Gesamtliste, Liste für Allergien, Alerts?</t>
+    <t>Referenz auf einen Eintrag.</t>
   </si>
   <si>
     <t>A reference to the actual resource from which data was derived.</t>
@@ -869,10 +877,106 @@
     <t>.target or .role or .role.entity</t>
   </si>
   <si>
+    <t>List.entry.item.id</t>
+  </si>
+  <si>
+    <t>List.entry.item.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>List.entry.item.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>List.entry.item.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>List.entry.item.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>List.entry.item.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Für Patient gibt es zurzeit keine Einträge</t>
+    <t>Begründung, warum die Summary-Liste leer ist.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -1212,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL30"/>
+  <dimension ref="A1:AL36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.04296875" customWidth="true" bestFit="true"/>
@@ -1225,7 +1329,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="186.796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="194.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1243,7 +1347,7 @@
     <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2353,10 +2457,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2491,7 +2595,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>21</v>
@@ -2509,11 +2613,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2546,18 +2652,18 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2583,23 +2689,23 @@
         <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>21</v>
@@ -2617,13 +2723,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2641,7 +2747,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2656,18 +2762,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2690,17 +2796,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2713,7 +2819,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2749,7 +2855,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2764,7 +2870,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -2772,10 +2878,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2798,19 +2904,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2835,11 +2941,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2857,7 +2963,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2872,18 +2978,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2906,19 +3012,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2967,7 +3073,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2982,18 +3088,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3016,13 +3122,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3073,7 +3179,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3088,18 +3194,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3122,19 +3228,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3183,7 +3289,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3198,22 +3304,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3232,19 +3338,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3293,7 +3399,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3308,18 +3414,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3342,19 +3448,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3382,10 +3488,10 @@
         <v>109</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3403,7 +3509,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3418,7 +3524,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3426,10 +3532,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3452,13 +3558,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3509,7 +3615,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3524,7 +3630,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3532,10 +3638,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3558,16 +3664,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3617,7 +3723,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3626,13 +3732,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3640,10 +3746,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3666,13 +3772,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3723,7 +3829,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3738,7 +3844,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3746,10 +3852,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3778,7 +3884,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3831,7 +3937,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3846,7 +3952,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3854,14 +3960,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3883,10 +3989,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3941,7 +4047,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3964,10 +4070,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3990,19 +4096,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4027,13 +4133,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4051,7 +4157,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4066,7 +4172,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4074,10 +4180,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4100,71 +4206,71 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4172,13 +4278,13 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4186,10 +4292,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4212,17 +4318,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4271,7 +4377,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4286,7 +4392,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4294,10 +4400,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4320,13 +4426,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4377,7 +4483,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4392,18 +4498,18 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4417,7 +4523,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4426,20 +4532,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4463,51 +4565,701 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AC31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AK32" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL30">
+  <autoFilter ref="A1:AL36">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4517,7 +5269,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI29">
+  <conditionalFormatting sqref="A2:AI35">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -592,7 +592,7 @@
     <t>List.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -666,7 +666,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -988,7 +988,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-list-emptyreason-vs</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1329,7 +1329,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="194.53125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="201.296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1344,7 +1344,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.66015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -482,7 +482,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Liste.</t>
+    <t>Status der Liste.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -512,7 +512,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt und hat daher den festen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -670,8 +670,8 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA ist sie eindeutig über den GDA-Index identifiziert und zum Zugriff auf die ELGA-Anwendung des Patienten berechtigt. 
+ Im Falle eines Patienten erfolgt die eindeutige Identifizierung über den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -824,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
+    <t>Eine Kennzeichnung des Eintrags als gelöscht ist nicht zulässig (siehe Invariant list-emptyreason-required).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -849,7 +849,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
+    <t>Das Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird. Dokumentiert wird das Datum der letzten Aktualisierung der Liste (List.date).</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|Device)
 </t>
   </si>
   <si>
@@ -1329,7 +1329,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="201.296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="207.19921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
